--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486290_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486290_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.503</v>
+        <v>8.167999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5988</v>
+        <v>6.2946</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9043</v>
+        <v>1.8734</v>
       </c>
       <c r="G2" t="n">
         <v>3.8977</v>
@@ -610,13 +610,13 @@
         <v>3.0451</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.0321</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0274</v>
+        <v>-0.3317</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3303</v>
+        <v>0.2995</v>
       </c>
       <c r="V2" t="n">
         <v>4.5199</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0146</v>
+        <v>7.6418</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9887</v>
+        <v>6.616</v>
       </c>
       <c r="F3" t="n">
         <v>1.0259</v>
@@ -688,10 +688,10 @@
         <v>3.0451</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5225</v>
+        <v>-0.8953</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4264</v>
+        <v>-0.7991</v>
       </c>
       <c r="U3" t="n">
         <v>-0.0961</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.287</v>
+        <v>2.8711</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2397</v>
+        <v>1.8237</v>
       </c>
       <c r="F4" t="n">
         <v>1.0473</v>
@@ -766,10 +766,10 @@
         <v>3.4801</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0755</v>
+        <v>-0.4915</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4264</v>
+        <v>-0.8424</v>
       </c>
       <c r="U4" t="n">
         <v>0.3509</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2849</v>
+        <v>1.888</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2279</v>
+        <v>0.8927</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0569</v>
+        <v>0.9953</v>
       </c>
       <c r="G5" t="n">
         <v>0.3341</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0291</v>
+        <v>-0.426</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0721</v>
+        <v>-0.2632</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1012</v>
+        <v>-0.1628</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8646</v>
+        <v>1.5776</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6588</v>
+        <v>1.1252</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2058</v>
+        <v>0.4523</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3915</v>
@@ -922,13 +922,13 @@
         <v>2.8276</v>
       </c>
       <c r="S6" t="n">
-        <v>0.168</v>
+        <v>-0.119</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3377</v>
+        <v>-0.1959</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1697</v>
+        <v>0.0769</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7395</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4998</v>
+        <v>1.0935</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2166</v>
+        <v>-1.1913</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7164</v>
+        <v>2.2848</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0605</v>
@@ -1000,13 +1000,13 @@
         <v>3.0451</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6028</v>
+        <v>0.1965</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3389</v>
+        <v>-0.3136</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9416</v>
+        <v>0.5101</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.1924</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.8393</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9084</v>
+        <v>1.0317</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9702</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6388</v>
+        <v>-0.447</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.274</v>
+        <v>-0.2055</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3648</v>
+        <v>-0.2415</v>
       </c>
       <c r="V9" t="n">
         <v>0.7395</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0814</v>
+        <v>-1.9581</v>
       </c>
       <c r="E10" t="n">
         <v>-0.3161</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7653</v>
+        <v>-1.642</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1484</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1303</v>
+        <v>-1.007</v>
       </c>
       <c r="T10" t="n">
         <v>-0.6165</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5138</v>
+        <v>-0.3906</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4136</v>
+        <v>-2.8299</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2224</v>
+        <v>-1.6694</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1912</v>
+        <v>-1.1604</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2287</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0326</v>
+        <v>-0.3836</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2656</v>
+        <v>-0.1815</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.233</v>
+        <v>-0.2022</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5649999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.475</v>
+        <v>19.1599</v>
       </c>
       <c r="E12" t="n">
-        <v>12.051</v>
+        <v>12.7361</v>
       </c>
       <c r="F12" t="n">
-        <v>6.423999999999999</v>
+        <v>6.423800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>7.649799999999999</v>
@@ -1390,13 +1390,13 @@
         <v>21.7506</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.289899999999999</v>
+        <v>-3.605</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.434200000000001</v>
+        <v>-3.7494</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1442</v>
+        <v>0.1441999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>2.0647</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4256</v>
+        <v>1.8418</v>
       </c>
       <c r="E13" t="n">
-        <v>1.321</v>
+        <v>1.768</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1047</v>
+        <v>0.0738</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0573</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0479</v>
+        <v>0.4642</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.536</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5839</v>
+        <v>0.5531</v>
       </c>
       <c r="V13" t="n">
         <v>1.13</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.658</v>
+        <v>-0.6502</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2239</v>
+        <v>-0.0003</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4341</v>
+        <v>-0.6499</v>
       </c>
       <c r="G14" t="n">
         <v>-1.9321</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4041</v>
+        <v>0.4119</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1456</v>
+        <v>0.9298</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.249</v>
+        <v>-0.915</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5397999999999999</v>
+        <v>2.2139</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-3.1288</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5987</v>
+        <v>1.7684</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7816</v>
+        <v>1.5691</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.3803</v>
+        <v>0.1992</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3499</v>
+        <v>4.7879</v>
       </c>
       <c r="K15" t="n">
-        <v>0.949</v>
+        <v>2.7009</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2989</v>
+        <v>2.087</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2488</v>
+        <v>-3.0196</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1674</v>
+        <v>-1.1318</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0814</v>
+        <v>-1.8878</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4373</v>
+        <v>0.6657</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9852</v>
+        <v>-0.2451</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4521</v>
+        <v>0.9109</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-2.044</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.1538</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3993</v>
+        <v>-1.749</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8786</v>
+        <v>-0.4436</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2778</v>
+        <v>-1.3054</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7684</v>
+        <v>-0.1681</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5691</v>
+        <v>0.514</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1992</v>
+        <v>-0.6821</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7879</v>
+        <v>0.5706</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7009</v>
+        <v>0.5324</v>
       </c>
       <c r="L16" t="n">
-        <v>2.087</v>
+        <v>0.0382</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0196</v>
+        <v>-0.7388</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1318</v>
+        <v>-0.0184</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8878</v>
+        <v>-0.7204</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1815</v>
+        <v>0.1794</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5804</v>
+        <v>0.0733</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7619</v>
+        <v>0.106</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.044</v>
+        <v>-1.3252</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1538</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8902</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7897</v>
+        <v>-1.791</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4693</v>
+        <v>-0.8045</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3204</v>
+        <v>-0.9865</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6694</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4898</v>
+        <v>0.4885</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3581</v>
+        <v>0.0228</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1317</v>
+        <v>0.4656</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2025</v>
+        <v>-1.9277</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7789</v>
+        <v>-1.1704</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4236</v>
+        <v>-0.7574</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1681</v>
+        <v>5.0908</v>
       </c>
       <c r="H18" t="n">
-        <v>0.514</v>
+        <v>3.458</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6821</v>
+        <v>1.6328</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5706</v>
+        <v>6.6823</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5324</v>
+        <v>3.9268</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>2.7556</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7388</v>
+        <v>-1.5916</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0184</v>
+        <v>-0.4688</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7204</v>
+        <v>-1.1228</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.435</v>
+        <v>-7.3952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-8.7003</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2741</v>
+        <v>0.3767</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.262</v>
+        <v>-0.2824</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0121</v>
+        <v>0.6591</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7087</v>
+        <v>-2.4167</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6174</v>
+        <v>-1.7691</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0913</v>
+        <v>-0.6476</v>
       </c>
       <c r="G19" t="n">
-        <v>5.0908</v>
+        <v>-2.5987</v>
       </c>
       <c r="H19" t="n">
-        <v>3.458</v>
+        <v>0.7816</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6328</v>
+        <v>-3.3803</v>
       </c>
       <c r="J19" t="n">
-        <v>6.6823</v>
+        <v>-0.3499</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9268</v>
+        <v>0.949</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7556</v>
+        <v>-1.2989</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5916</v>
+        <v>-2.2488</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4688</v>
+        <v>-0.1674</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1228</v>
+        <v>-2.0814</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.3952</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-8.7003</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4043</v>
+        <v>1.2696</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7294</v>
+        <v>0.7559</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3252</v>
+        <v>0.5137</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9029</v>
+        <v>-3.6402</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-1.531</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0425</v>
+        <v>-2.1092</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7111</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2862</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4747</v>
+        <v>-0.1959</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8115</v>
+        <v>0.7447</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3904</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.9906</v>
+        <v>-6.4819</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1339</v>
+        <v>-4.6868</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8567</v>
+        <v>-1.795</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3721</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1216</v>
+        <v>0.6303</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.113</v>
+        <v>0.3341</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2346</v>
+        <v>0.2962</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5649999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-18.4751</v>
+        <v>-17.7299</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.423999999999999</v>
+        <v>-6.423799999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-12.0509</v>
+        <v>-11.306</v>
       </c>
       <c r="G22" t="n">
         <v>-7.6496</v>
@@ -2149,7 +2149,7 @@
         <v>10.4639</v>
       </c>
       <c r="L22" t="n">
-        <v>0.07589999999999986</v>
+        <v>0.07589999999999941</v>
       </c>
       <c r="M22" t="n">
         <v>-18.1899</v>
@@ -2167,16 +2167,16 @@
         <v>-21.7508</v>
       </c>
       <c r="R22" t="n">
-        <v>8.700000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>4.29</v>
+        <v>5.0352</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1442000000000001</v>
+        <v>-0.1440999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>4.4344</v>
+        <v>5.179099999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0646</v>
